--- a/public/Erection_Template.xlsx
+++ b/public/Erection_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 Work\01 IBIM\01 Working\2026-04\sequencing\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 Work\01 IBIM\05 website\sequencing\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -723,9 +723,6 @@
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -771,6 +768,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="23" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1148,159 +1148,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.625" customWidth="1"/>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.875" customWidth="1"/>
-    <col min="6" max="6" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.59765625" customWidth="1"/>
+    <col min="2" max="2" width="16.59765625" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.8984375" customWidth="1"/>
+    <col min="6" max="6" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.15" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" ht="37.200000000000003" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="8"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="8"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="8"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="8"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="8"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="7"/>
     </row>
-    <row r="10" spans="1:8" ht="28.5">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:8" ht="27.6">
+      <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="15"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
